--- a/paired-tag/latest/paired-tag.xlsx
+++ b/paired-tag/latest/paired-tag.xlsx
@@ -38,10 +38,10 @@
     </comment>
     <comment ref="B1" authorId="1">
       <text>
-        <t>A locally assigned identifier provided by the data provider for the dataset. It
-is used to reference an external metadata record that may be maintained
-independently, enabling traceability and supporting provenance tracking.
-Example: Visium_9OLC_A4_S1</t>
+        <t>An identifier assigned by the data provider to reference an external metadata
+record for the dataset. The external record may be maintained independently and
+can support dataset traceability and provenance tracking. Leave this field empty
+if no such identifier exists.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="1">
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="334">
   <si>
     <t>parent_sample_id</t>
   </si>
@@ -184,94 +184,322 @@
     <t>dataset_type</t>
   </si>
   <si>
+    <t>Cell DIVE</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
+  </si>
+  <si>
+    <t>CODEX</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
+  </si>
+  <si>
+    <t>Light Sheet</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
+  </si>
+  <si>
+    <t>MIBI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
+  </si>
+  <si>
+    <t>LC-MS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000194</t>
+  </si>
+  <si>
     <t>HiFi-Slide</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000195</t>
   </si>
   <si>
+    <t>Histology</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
+  </si>
+  <si>
+    <t>PhenoCycler</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000199</t>
+  </si>
+  <si>
+    <t>CyCIF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000200</t>
+  </si>
+  <si>
+    <t>MALDI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
+  </si>
+  <si>
+    <t>SIMS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
+  </si>
+  <si>
+    <t>DESI</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000204</t>
+  </si>
+  <si>
+    <t>Auto-fluorescence</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
+  </si>
+  <si>
+    <t>Confocal</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000206</t>
+  </si>
+  <si>
+    <t>Thick section Multiphoton MxIF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
+  </si>
+  <si>
+    <t>Second Harmonic Generation (SHG)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000208</t>
+  </si>
+  <si>
+    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
+  </si>
+  <si>
+    <t>10X Multiome</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000215</t>
+  </si>
+  <si>
+    <t>Molecular Cartography</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
+  </si>
+  <si>
+    <t>CosMx Transcriptomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000218</t>
+  </si>
+  <si>
+    <t>Xenium</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
+  </si>
+  <si>
+    <t>MERFISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000221</t>
+  </si>
+  <si>
     <t>SNARE-seq2</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000264</t>
   </si>
   <si>
+    <t>2D Imaging Mass Cytometry</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
+  </si>
+  <si>
+    <t>GeoMx (NGS)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
+  </si>
+  <si>
+    <t>GeoMx (nCounter)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
+  </si>
+  <si>
+    <t>Visium (no probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000302</t>
+  </si>
+  <si>
+    <t>Visium (with probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000303</t>
+  </si>
+  <si>
+    <t>ATACseq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000309</t>
+  </si>
+  <si>
+    <t>RNAseq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000310</t>
+  </si>
+  <si>
+    <t>RNAseq (with probes)</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
+  </si>
+  <si>
+    <t>nanoSPLITS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000312</t>
+  </si>
+  <si>
+    <t>MUSIC</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
+  </si>
+  <si>
+    <t>Resolve</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000384</t>
+  </si>
+  <si>
+    <t>Stereo-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000385</t>
+  </si>
+  <si>
+    <t>Seq-Scope</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000390</t>
+  </si>
+  <si>
+    <t>DART-FISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000396</t>
+  </si>
+  <si>
+    <t>seqFISH</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000397</t>
+  </si>
+  <si>
+    <t>MS Lipidomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
+  </si>
+  <si>
+    <t>CyTOF</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
+  </si>
+  <si>
+    <t>DBiT-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000428</t>
+  </si>
+  <si>
+    <t>Singular Genomics G4X</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000429</t>
+  </si>
+  <si>
+    <t>CosMx Proteomics</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000435</t>
+  </si>
+  <si>
+    <t>FACS</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
+  </si>
+  <si>
+    <t>Olink</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
+  </si>
+  <si>
+    <t>4i</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000447</t>
+  </si>
+  <si>
+    <t>MPLEx</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000448</t>
+  </si>
+  <si>
+    <t>Pixel-seqV2</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
+  </si>
+  <si>
+    <t>Visium HD</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000451</t>
+  </si>
+  <si>
     <t>COMET</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000458</t>
   </si>
   <si>
-    <t>Visium (no probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000302</t>
-  </si>
-  <si>
-    <t>DESI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000204</t>
-  </si>
-  <si>
-    <t>Confocal</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000206</t>
-  </si>
-  <si>
-    <t>Stereo-seq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000385</t>
-  </si>
-  <si>
-    <t>Visium (with probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000303</t>
-  </si>
-  <si>
-    <t>Molecular Cartography</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
-  </si>
-  <si>
     <t>Virtual Histology</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000473</t>
   </si>
   <si>
-    <t>DBiT-seq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000428</t>
-  </si>
-  <si>
-    <t>Seq-Scope</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000390</t>
-  </si>
-  <si>
-    <t>CosMx Transcriptomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000218</t>
-  </si>
-  <si>
-    <t>CyCIF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000200</t>
-  </si>
-  <si>
-    <t>Light Sheet</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
+    <t>Raman Imaging</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000475</t>
+  </si>
+  <si>
+    <t>STARmap</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000476</t>
   </si>
   <si>
     <t>iCLAP</t>
@@ -280,112 +508,16 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000479</t>
   </si>
   <si>
-    <t>seqFISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000397</t>
-  </si>
-  <si>
-    <t>ATACseq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000309</t>
-  </si>
-  <si>
-    <t>CosMx Proteomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000435</t>
-  </si>
-  <si>
-    <t>Singular Genomics G4X</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000429</t>
-  </si>
-  <si>
-    <t>Visium HD</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000451</t>
-  </si>
-  <si>
-    <t>MERFISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000221</t>
-  </si>
-  <si>
-    <t>10X Multiome</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000215</t>
-  </si>
-  <si>
-    <t>4i</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000447</t>
-  </si>
-  <si>
-    <t>PhenoCycler</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000199</t>
-  </si>
-  <si>
-    <t>Second Harmonic Generation (SHG)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000208</t>
-  </si>
-  <si>
-    <t>Thick section Multiphoton MxIF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
-  </si>
-  <si>
     <t>MACSima</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000480</t>
   </si>
   <si>
-    <t>CyTOF</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000407</t>
-  </si>
-  <si>
-    <t>Olink</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000441</t>
-  </si>
-  <si>
-    <t>MIBI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000172</t>
-  </si>
-  <si>
-    <t>Auto-fluorescence</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000205</t>
-  </si>
-  <si>
-    <t>FACS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000440</t>
-  </si>
-  <si>
-    <t>Xenium</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
+    <t>Illumina Spatial ver0</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
   </si>
   <si>
     <t>DNA Methylation</t>
@@ -394,142 +526,22 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000490</t>
   </si>
   <si>
-    <t>SIMS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000202</t>
-  </si>
-  <si>
-    <t>Cell DIVE</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000159</t>
-  </si>
-  <si>
-    <t>CODEX</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000160</t>
-  </si>
-  <si>
-    <t>GeoMx (NGS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000300</t>
-  </si>
-  <si>
-    <t>MUSIC</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000328</t>
-  </si>
-  <si>
-    <t>Pixel-seqV2</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000450</t>
-  </si>
-  <si>
-    <t>MALDI</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000201</t>
-  </si>
-  <si>
-    <t>2D Imaging Mass Cytometry</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000296</t>
-  </si>
-  <si>
-    <t>Histology</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000197</t>
-  </si>
-  <si>
-    <t>Enhanced Stimulated Raman Spectroscopy (SRS)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
-  </si>
-  <si>
-    <t>Illumina Spatial ver0</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
-  </si>
-  <si>
-    <t>DART-FISH</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000396</t>
-  </si>
-  <si>
-    <t>Resolve</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000384</t>
-  </si>
-  <si>
-    <t>RNAseq</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000310</t>
-  </si>
-  <si>
-    <t>LC-MS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000194</t>
-  </si>
-  <si>
-    <t>nanoSPLITS</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000312</t>
-  </si>
-  <si>
-    <t>GeoMx (nCounter)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
-  </si>
-  <si>
-    <t>Raman Imaging</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000475</t>
-  </si>
-  <si>
-    <t>RNAseq (with probes)</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
-  </si>
-  <si>
     <t>Paired-Tag</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000492</t>
   </si>
   <si>
-    <t>MS Lipidomics</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
-  </si>
-  <si>
-    <t>STARmap</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000476</t>
-  </si>
-  <si>
-    <t>MPLEx</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000448</t>
+    <t>snm3C-seq</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000504</t>
+  </si>
+  <si>
+    <t>Whole Exome Sequencing</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000514</t>
   </si>
   <si>
     <t>contributors_path</t>
@@ -541,214 +553,244 @@
     <t>library_preparation_kit</t>
   </si>
   <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C65167</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000250</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000251</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000260</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000261</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000265</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000299</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000320</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 6.5mm, 4 reactions; PN 1000520</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000321</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000322</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000334</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000335</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 8 rxns; PN 1000370</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000336</t>
   </si>
   <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000337</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000338</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000339</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000340</t>
+  </si>
+  <si>
+    <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000341</t>
+  </si>
+  <si>
+    <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000342</t>
+  </si>
+  <si>
+    <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000343</t>
+  </si>
+  <si>
+    <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000344</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000355</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000365</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 4 rxns; PN 1000298</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000366</t>
   </si>
   <si>
+    <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000374</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000375</t>
+  </si>
+  <si>
+    <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000377</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000394</t>
+  </si>
+  <si>
+    <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000398</t>
+  </si>
+  <si>
+    <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000399</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium GEM-X Single Cell 3' Kit v4, 16 rxns; PN 1000691</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000400</t>
+  </si>
+  <si>
+    <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000432</t>
+  </si>
+  <si>
+    <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000439</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000460</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000466</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000467</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000469</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000471</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium Next GEM Single Cell Fixed RNA Sample Preparation Kit, 16 rxns; PN 1000414</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000484</t>
   </si>
   <si>
-    <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 4 slides, 16 reactions; PN 1000184</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000261</t>
-  </si>
-  <si>
-    <t>Parse Biosciences; Evercode WT v2 Kit, 48 rxns; PN ECW02030</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000341</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 16 rxns; PN 1000263</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000339</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Human Transcriptome, 1 slides, 4 reactions; PN 1000338</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000320</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 16 rxns; PN 1000268</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000337</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Next GEM Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000175</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000471</t>
-  </si>
-  <si>
-    <t>10x Genomics; Library Construction Kit C, 16 rxns; PN 1000694</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000399</t>
-  </si>
-  <si>
-    <t>10x Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Mouse Transcriptome, 6.5mm, 4 rxns; PN 1000521</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000432</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 3' HT Kit v3.1, 48 rxns; PN 1000348</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000335</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 3' GEM, Library &amp; Gel Bead Kit v3.1, 16 rxns; PN 1000121</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000334</t>
-  </si>
-  <si>
-    <t>10x Genomics; Library Construction Kit C, 4 rxns; PN 1000689</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000398</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 11 mm, 2 reactions; PN 1000522</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000322</t>
-  </si>
-  <si>
-    <t>Illumina; TruSeq Stranded mRNA Library Prep (48 samples); PN 20020594</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000343</t>
-  </si>
-  <si>
-    <t>10X Genomics; Automated Library Construction Kit, 24 rxns; PN 1000428</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000374</t>
-  </si>
-  <si>
-    <t>New England BioLabs; NEBNext Ultra II RNA Library Prep Kit for Illumina; PN E7770</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000377</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Automated Single Cell 5' Kit v2, 24 rxns; PN 1000290</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000365</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium Spatial Gene Expression Slide and Reagent Kit, 1 slides, 4 reactions; PN 1000187</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000265</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium GEM-X Single Cell 5' Kit v3, 16 rxns; PN 1000699</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000394</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Single Cell ATAC Library &amp; Gel Bead Kit, 16 rxns; PN 1000110</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000469</t>
-  </si>
-  <si>
-    <t>10x Genomics; Library Construction Kit, 16 rxns; PN 1000190</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000439</t>
-  </si>
-  <si>
-    <t>Parse Biosciences; Evercode WT Mini v2 Kit, 12 rxns; PN ECW02010</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000342</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 48 rxns; PN 1000356</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000467</t>
-  </si>
-  <si>
-    <t>Illumina; TruSeq Stranded mRNA Library Prep (96 samples); PN 20020595</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000344</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 5' Kit v2, 4 rxns; PN 1000265</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000340</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 4 rxn; PN 1000285</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000251</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell Fixed RNA Hybridization &amp; Library Kit, 4 rxns; PN 1000415</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000375</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C65167</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Single Cell 3' GEM, Library &amp; Gel Bead Kit v3, 4 rxns; PN 1000092</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000260</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Single Cell 3ʹ GEM, Library &amp; Gel Bead Kit v3, 16 rxns; PN 1000075</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000460</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Single Cell 3' Library &amp; Gel Bead Kit, 4 rxns; PN 120267</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000299</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium Spatial for FFPE Gene Expression Kit, Mouse Transcriptome, 4 rxns; PN 1000339</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000355</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium NextGem Single Cell Multiome ATAC + Gene Expression Reagent Bundle, 16 rxn; PN 1000283</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000250</t>
+    <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000497</t>
   </si>
   <si>
     <t>Epigenome Technologies; Multiplex Droplet Paired-Tag 16 Reaction Kit; PN MDP16101</t>
@@ -757,28 +799,10 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000499</t>
   </si>
   <si>
-    <t>10X Genomics; Chromium Next GEM Single Cell 3' Kit v3.1, 4 rxns; PN 1000269</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000338</t>
-  </si>
-  <si>
-    <t>10x Genomics; GEM-X Flex GEM &amp; Library Kit, 4 rxns; PN 1000782</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000497</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Next GEM Single Cell 5' HT Kit v2, 8 rxns; PN 1000374</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000466</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium CytAssist Spatial Gene Expression for FFPE, Human Transcriptome, 6.5mm, 4 reactions; PN 1000520</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000321</t>
+    <t>Takara Bio; SMART-Seq Total RNA Library Prep with ZapR Depletion (with UMIs), 96 rxns; PN 634355</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000507</t>
   </si>
   <si>
     <t>capture_batch_id</t>
@@ -793,22 +817,58 @@
     <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C126386</t>
   </si>
   <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C48660</t>
+  </si>
+  <si>
+    <t>Thermo Fisher Scientific</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_008452</t>
+  </si>
+  <si>
+    <t>Hamamatsu</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_017105</t>
+  </si>
+  <si>
     <t>Leica Biosystems</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_023603</t>
   </si>
   <si>
-    <t>Not applicable</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C48660</t>
-  </si>
-  <si>
-    <t>Thermo Fisher Scientific</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_008452</t>
+    <t>Ionpath</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023605</t>
+  </si>
+  <si>
+    <t>10x Genomics</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023672</t>
+  </si>
+  <si>
+    <t>HTX Technologies</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023734</t>
+  </si>
+  <si>
+    <t>Akoya Biosciences</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023774</t>
+  </si>
+  <si>
+    <t>SunChrom</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023908</t>
   </si>
   <si>
     <t>Roche Diagnostics</t>
@@ -817,55 +877,91 @@
     <t>https://identifiers.org/RRID:SCR_025096</t>
   </si>
   <si>
-    <t>HTX Technologies</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023734</t>
-  </si>
-  <si>
-    <t>10x Genomics</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023672</t>
-  </si>
-  <si>
-    <t>Hamamatsu</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_017105</t>
-  </si>
-  <si>
-    <t>Ionpath</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023605</t>
-  </si>
-  <si>
-    <t>Akoya Biosciences</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023774</t>
-  </si>
-  <si>
-    <t>SunChrom</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023908</t>
-  </si>
-  <si>
     <t>preparation_instrument_model</t>
   </si>
   <si>
+    <t>Chromium Controller</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_019326</t>
+  </si>
+  <si>
+    <t>Sublimator</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023729</t>
+  </si>
+  <si>
+    <t>M3+ Sprayer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023731</t>
+  </si>
+  <si>
+    <t>TM-Sprayer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023732</t>
+  </si>
+  <si>
+    <t>M5 Sprayer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023733</t>
+  </si>
+  <si>
     <t>NanoZoomer S210</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_023760</t>
   </si>
   <si>
-    <t>Sublimator</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023729</t>
+    <t>NanoZoomer S360</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023761</t>
+  </si>
+  <si>
+    <t>NanoZoomer S60</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023762</t>
+  </si>
+  <si>
+    <t>SunCollect Sprayer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023907</t>
+  </si>
+  <si>
+    <t>AutoStainer XL</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023957</t>
+  </si>
+  <si>
+    <t>Chromium iX</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024536</t>
+  </si>
+  <si>
+    <t>Chromium X</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024537</t>
+  </si>
+  <si>
+    <t>Visium CytAssist</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_024570</t>
+  </si>
+  <si>
+    <t>ST5020 Multistainer</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_025021</t>
   </si>
   <si>
     <t>EVOS M7000</t>
@@ -874,169 +970,109 @@
     <t>https://identifiers.org/RRID:SCR_025070</t>
   </si>
   <si>
-    <t>Chromium Controller</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_019326</t>
-  </si>
-  <si>
-    <t>NanoZoomer S360</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023761</t>
-  </si>
-  <si>
-    <t>NanoZoomer S60</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023762</t>
-  </si>
-  <si>
-    <t>Chromium X</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024537</t>
-  </si>
-  <si>
-    <t>AutoStainer XL</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023957</t>
-  </si>
-  <si>
-    <t>Visium CytAssist</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024570</t>
-  </si>
-  <si>
-    <t>SunCollect Sprayer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023907</t>
-  </si>
-  <si>
-    <t>M3+ Sprayer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023731</t>
-  </si>
-  <si>
     <t>Discovery Ultra</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_025097</t>
   </si>
   <si>
-    <t>ST5020 Multistainer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_025021</t>
-  </si>
-  <si>
-    <t>Chromium iX</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_024536</t>
-  </si>
-  <si>
     <t>Chromium Connect</t>
   </si>
   <si>
     <t>https://identifiers.org/RRID:SCR_025146</t>
   </si>
   <si>
-    <t>M5 Sprayer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023733</t>
-  </si>
-  <si>
-    <t>TM-Sprayer</t>
-  </si>
-  <si>
-    <t>https://identifiers.org/RRID:SCR_023732</t>
-  </si>
-  <si>
     <t>preparation_instrument_kit</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 48 rxns; PN 1000234</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000262</t>
+  </si>
+  <si>
+    <t>10x Genomics; Chromium Next GEM Chip J Single Cell Kit, 16 rxns; PN 1000230</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000263</t>
+  </si>
+  <si>
+    <t>10X Genomics; Visium FFPE Reagent Kit v2-Small, PN 1000436</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000324</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Chip Q Single Cell Kit, 16 rxns; PN 1000422</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 48 rxns; PN 1000286</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000367</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 16 rxns; PN 1000287</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000368</t>
+  </si>
+  <si>
     <t>10X Genomics; Chromium Next GEM Chip K Automated Single Cell Kit, 48 rxns; PN 1000289</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000373</t>
   </si>
   <si>
+    <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 48 rxns; PN 1000120</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000378</t>
+  </si>
+  <si>
+    <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 16 rxns; PN 1000127</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000379</t>
+  </si>
+  <si>
     <t>10x Genomics; Chromium Single Cell B Chip Kit, 16 rxns; PN 1000074</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000462</t>
   </si>
   <si>
+    <t>10x Genomics; Chromium Chip E Single Cell ATAC Kit, 48 rxns; PN 1000155</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000470</t>
+  </si>
+  <si>
+    <t>10x Genomics; Visium HD, Human Transcriptome, 6.5 mm, 4 runs; PN 1000675</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000493</t>
+  </si>
+  <si>
     <t>10x Genomics; Visium HD, Mouse Transcriptome, 6.5 mm, 4 runs; PN 1000676</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000494</t>
   </si>
   <si>
-    <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 48 rxns; PN 1000286</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000367</t>
-  </si>
-  <si>
-    <t>10x Genomics; Chromium Chip E Single Cell ATAC Kit, 48 rxns; PN 1000155</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000470</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 48 rxns; PN 1000120</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000378</t>
-  </si>
-  <si>
-    <t>10x Genomics; Visium HD, Human Transcriptome, 6.5 mm, 4 runs; PN 1000675</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000493</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Chip K Single Cell Kit, 16 rxns; PN 1000287</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000368</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Chip G Single Cell Kit, 16 rxns; PN 1000127</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000379</t>
-  </si>
-  <si>
     <t>10x Genomics; Visium HD, Human Transcriptome, 11 mm, 4 runs; PN 1001037</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000495</t>
   </si>
   <si>
-    <t>10x Genomics; Chromium GEM-X Single Cell 3' Kit v4, 16 rxns; PN 1000691</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000400</t>
-  </si>
-  <si>
-    <t>10X Genomics; Visium FFPE Reagent Kit v2-Small, PN 1000436</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000324</t>
-  </si>
-  <si>
-    <t>10X Genomics; Chromium Next GEM Chip Q Single Cell Kit, 16 rxns; PN 1000422</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000325</t>
+    <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000496</t>
   </si>
   <si>
     <t>10x Genomics; GEM-X Flex Gene Expression Chip Kit, 4 chips; PN 1000791</t>
@@ -1045,12 +1081,6 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000498</t>
   </si>
   <si>
-    <t>10x Genomics; Visium HD, Mouse Transcriptome, 11 mm, 4 runs; PN 1001038</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000496</t>
-  </si>
-  <si>
     <t>number_of_pre_amplification_pcr_cycles</t>
   </si>
   <si>
@@ -1075,6 +1105,18 @@
     <t>antibody_reagent_kit</t>
   </si>
   <si>
+    <t>Standard BioTools; Maxpar Phosphoprotein Staining Kit; PN 201604</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000408</t>
+  </si>
+  <si>
+    <t>Standard BioTools; Maxpar Nuclear Antigen Staining Kit; PN 201603</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000409</t>
+  </si>
+  <si>
     <t>Standard BioTools; Maxpar Cytoplasmic/Secreted Antigen Staining Kit; PN 201602</t>
   </si>
   <si>
@@ -1087,36 +1129,24 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000411</t>
   </si>
   <si>
+    <t>Abcam; Anti-Histone H3 (tri methyl K27) antibody [mAbcam6002]- ChIP Grade; PN ab6002</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000500</t>
+  </si>
+  <si>
+    <t>Abcam; Anti-Histone H3 (acetyl K27) antibody [EP16602] - ChIP Grade; PN ab177178</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000501</t>
+  </si>
+  <si>
     <t>Abcam; Anti-Histone H3 (tri methyl K9) antibody [EPR16601] - ChIP Grade; PN ab176916</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000502</t>
   </si>
   <si>
-    <t>Abcam; Anti-Histone H3 (acetyl K27) antibody [EP16602] - ChIP Grade; PN ab177178</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000501</t>
-  </si>
-  <si>
-    <t>Abcam; Anti-Histone H3 (tri methyl K27) antibody [mAbcam6002]- ChIP Grade; PN ab6002</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000500</t>
-  </si>
-  <si>
-    <t>Standard BioTools; Maxpar Nuclear Antigen Staining Kit; PN 201603</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000409</t>
-  </si>
-  <si>
-    <t>Standard BioTools; Maxpar Phosphoprotein Staining Kit; PN 201604</t>
-  </si>
-  <si>
-    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000408</t>
-  </si>
-  <si>
     <t>metadata_schema_id</t>
   </si>
   <si>
@@ -1135,7 +1165,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-07-27T11:31:05-07:00</t>
+    <t>2026-10-21T13:37:22-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -1260,57 +1290,57 @@
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>315</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2">
       <c r="D2" t="s" s="5">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="P2" t="s" s="17">
-        <v>316</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="8">
     <dataValidation type="list" sqref="D2:D1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$58</formula1>
+      <formula1>'dataset_type'!$A$1:$A$60</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="G2:G1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'library_preparation_kit'!$A$1:$A$40</formula1>
+      <formula1>'library_preparation_kit'!$A$1:$A$42</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
       <formula1>'preparation_instrument_vendor'!$A$1:$A$11</formula1>
@@ -1319,7 +1349,7 @@
       <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="K2:K1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_kit'!$A$1:$A$18</formula1>
+      <formula1>'preparation_instrument_kit'!$A$1:$A$20</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="between" sqref="L2:L1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-2147483648</formula1>
@@ -1340,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1805,6 +1835,22 @@
       </c>
       <c r="B58" t="s" s="0">
         <v>119</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1814,327 +1860,343 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>202</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2149,90 +2211,90 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2247,154 +2309,154 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>229</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>210</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>182</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>243</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -2404,151 +2466,167 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>263</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>264</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>265</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>266</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>178</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>181</v>
+        <v>279</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>182</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>191</v>
+        <v>287</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>192</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>282</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>292</v>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>299</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -2563,22 +2641,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>298</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -2593,66 +2671,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>301</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>302</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>181</v>
+        <v>319</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>182</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>314</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -2673,30 +2751,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
